--- a/req3-device/excel/HW01_TestCases.xlsx
+++ b/req3-device/excel/HW01_TestCases.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -486,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="5.44140625" customWidth="1" min="1" max="1"/>
@@ -565,6 +567,23 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Lồng bảo vệ, dây điện/phích cắm, cánh quạt, góc nghiêng, mặt đặt nghiêng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Điều khiển đảo gió</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bật hoặc ngừng chuyển động đảo hướng của đầu quạt trong khi cánh quạt vẫn hoạt động.</t>
         </is>
       </c>
     </row>
@@ -582,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25.88671875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -593,7 +612,7 @@
     <col width="13.6640625" customWidth="1" min="8" max="9"/>
     <col width="11.88671875" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -676,7 +695,7 @@
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
     </row>
-    <row r="3" ht="110" customHeight="1">
+    <row r="3" ht="125" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>01 - 001</t>
@@ -707,10 +726,14 @@
 3. Không có tiếng lạ hoặc mùi khét</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Như expected</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Untested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -718,14 +741,21 @@
           <t>23120031</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n"/>
+      <c r="I3" s="3" t="n">
+        <v>46295</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="110" customHeight="1">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/et3gtzuObck?feature=share</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="125" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>01 - 002</t>
@@ -754,7 +784,7 @@
 2. Quạt không tắt giữa các lần chuyển</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Untested</t>
@@ -772,7 +802,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="110" customHeight="1">
+    <row r="5" ht="125" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>01 - 003</t>
@@ -801,7 +831,7 @@
 2. Quạt không tắt giữa các lần chuyển</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Untested</t>
@@ -819,7 +849,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="110" customHeight="1">
+    <row r="6" ht="125" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
           <t>01 - 004</t>
@@ -850,10 +880,14 @@
 3. Không có tiếng va chạm hoặc tiếng lạ khi dừng</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Như expected</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Untested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -861,14 +895,21 @@
           <t>23120031</t>
         </is>
       </c>
-      <c r="I6" s="3" t="n"/>
+      <c r="I6" s="3" t="n">
+        <v>46295</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="110" customHeight="1">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/1sZU2MDkQWU?feature=share</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="125" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>01 - 005</t>
@@ -876,32 +917,39 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Nhấn đổi nút liên tục và nhanh</t>
+          <t>Nhấn đồng thời hai nút tốc độ 1 và 2 khi quạt không có điện</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Quạt cắm điện, đang tắt.</t>
+          <t>Không thực hiện khi quạt đang có điện; không dùng lực mạnh.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1. Nhấn liên tục các nút theo thứ tự 1, 2, 3, Off, lặp lại khoảng 20 lần trong 10 giây
-2. Dừng ở nút tốc độ 2 và quan sát quạt 10 giây
-(Input: Nhấn xen kẽ các nút 1, 2, 3, Off khoảng 20 lần trong 10 giây.)</t>
+          <t>1. Rút phích cắm và xác nhận quạt không có điện
+2. Dùng hai ngón tay nhấn nhẹ đồng thời nút 1 và nút 2
+3. Thả tay và quan sát trạng thái hai nút
+4. Nhấn nút Off để đưa quạt về trạng thái ban đầu
+(Input: Dùng hai ngón tay nhấn nhẹ nút tốc độ 1 và 2 cùng lúc.)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1. Nút không bị kẹt hoặc không nhả
-2. Quạt chạy đúng theo nút được nhấn cuối cùng
-3. Không có tia lửa, mùi khét; cầu dao không nhảy</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
+          <t>1. Không có trường hợp cả hai nút tốc độ cùng bị giữ ở trạng thái nhấn
+2. Tối đa một nút được giữ, hoặc cả hai đều nhả
+3. Các nút không bị kẹt, lún hoặc hư hỏng
+4. Nút Off đưa cơ cấu về trạng thái tắt bình thường</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Fail. Hai nút cùng lún xuống</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Untested</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -909,10 +957,22 @@
           <t>23120031</t>
         </is>
       </c>
-      <c r="I7" s="3" t="n"/>
+      <c r="I7" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>AI chỉ kiểm tra nhấn các nút liên tiếp, không kiểm tra hai nút được nhấn đồng thời.</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/NjJz7VyT0h4</t>
         </is>
       </c>
     </row>
@@ -934,7 +994,7 @@
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
     </row>
-    <row r="9" ht="110" customHeight="1">
+    <row r="9" ht="125" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
           <t>02 - 001</t>
@@ -965,7 +1025,7 @@
 3. Tốc độ quay và tiếng ồn ổn định, quạt không tự tắt</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="n"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Untested</t>
@@ -983,7 +1043,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="110" customHeight="1">
+    <row r="10" ht="125" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
           <t>02 - 002</t>
@@ -1012,7 +1072,7 @@
 2. Không rung lắc mạnh, không đổ</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Untested</t>
@@ -1030,7 +1090,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="110" customHeight="1">
+    <row r="11" ht="125" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
           <t>02 - 003</t>
@@ -1059,7 +1119,7 @@
 2. Không có tiếng rít, cọ xát hoặc gõ lạch cạch ở cả 3 mức</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="n"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Untested</t>
@@ -1077,7 +1137,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="110" customHeight="1">
+    <row r="12" ht="125" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>02 - 004</t>
@@ -1106,7 +1166,7 @@
 2. Mức độ bay tăng dần theo tốc độ</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="n"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Untested</t>
@@ -1124,7 +1184,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="110" customHeight="1">
+    <row r="13" ht="125" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
           <t>02 - 005</t>
@@ -1132,32 +1192,40 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Chạy lại sau khi mất điện đột ngột</t>
+          <t>Cấp điện khi nút tốc độ 1 đã được chọn trong lúc quạt không có điện</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Quạt đang chạy ở tốc độ 2.</t>
+          <t>Không cắm/rút phích trực tiếp dưới tải nếu không có phương án cấp nguồn an toàn.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1. Rút phích cắm khi quạt đang chạy tốc độ 2
-2. Chờ 10 giây
-3. Cắm phích lại vào ổ điện, không thao tác nút
-(Input: Rút phích cắm, chờ 10 giây, cắm lại (nút vẫn ở tốc độ 2).)</t>
+          <t>1. Đặt quạt trên mặt phẳng ổn định
+2. Ngắt nguồn điện của quạt
+3. Nhấn nút tốc độ 1 khi quạt không có điện
+4. Đứng cách cánh và lồng quạt một khoảng an toàn
+5. Cấp điện lại bằng công tắc nguồn phù hợp
+6. Quan sát hoạt động của quạt trong 30 giây
+(Input: Ngắt nguồn, nhấn nút tốc độ 1, sau đó cấp điện lại bằng ổ cắm hoặc công tắc nguồn phù hợp.)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1. Quạt tự chạy lại ở tốc độ 2
-2. Không có tia lửa ở phích cắm hoặc ổ điện</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
+          <t>1. Quạt khởi động ở tốc độ 1 tương ứng với nút đã chọn
+2. Quạt chạy ổn định, không tự chuyển sang tốc độ khác
+3. Không có tiếng va chạm, mùi khét hoặc dấu hiệu bất thường</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Như expected</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Untested</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1165,10 +1233,22 @@
           <t>23120031</t>
         </is>
       </c>
-      <c r="I13" s="3" t="n"/>
+      <c r="I13" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>AI chỉ kiểm tra mất điện khi quạt đang chạy tốc độ 2; không kiểm tra việc chọn tốc độ trong trạng thái không có điện rồi mới cấp nguồn.</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/HRBWQmdAtM8?feature=share</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1270,7 @@
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
     </row>
-    <row r="15" ht="110" customHeight="1">
+    <row r="15" ht="125" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
           <t>03 - 001</t>
@@ -1220,7 +1300,7 @@
 2. Ngón tay không chạm được vào cánh quạt qua khe lưới</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="n"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Untested</t>
@@ -1238,7 +1318,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="110" customHeight="1">
+    <row r="16" ht="125" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
           <t>03 - 002</t>
@@ -1268,7 +1348,7 @@
 2. Không tự sụp hoặc trượt, khớp không kêu</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="n"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Untested</t>
@@ -1286,7 +1366,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="110" customHeight="1">
+    <row r="17" ht="125" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
           <t>03 - 003</t>
@@ -1317,7 +1397,7 @@
 3. Chân phích không cong, không gỉ hoặc đổi màu</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="n"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Untested</t>
@@ -1335,7 +1415,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="110" customHeight="1">
+    <row r="18" ht="125" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
           <t>03 - 004</t>
@@ -1366,7 +1446,7 @@
 3. Cánh không nứt, mẻ</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="n"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Untested</t>
@@ -1384,60 +1464,98 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="110" customHeight="1">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>03 - 005</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Vận hành trên mặt nghiêng nhẹ (khoảng 10°)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Tấm ván nghiêng khoảng 10° đặt ổn định; quạt đặt xa mép; tay sẵn sàng rút phích.</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1. Đặt quạt lên mặt nghiêng
-2. Bật tốc độ 1 trong 1 phút, quan sát
-3. Chuyển sang tốc độ 3 trong 1 phút, quan sát
-(Input: Chạy tốc độ 1 rồi tốc độ 3, mỗi mức 1 phút.)</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1. Quạt không tự trượt và không đổ
-2. Không có tiếng lạ</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Untested</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Function 04: Điều khiển đảo gió</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="125" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>04 - 001</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Ngừng đảo gió khi quạt đang chạy</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>không dùng lực nếu nút bị cứng.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1. Đặt quạt trên mặt phẳng ổn định
+2. Bật quạt ở tốc độ 1
+3. Bật chức năng đảo gió và chờ đầu quạt đảo ít nhất một chu kỳ
+4. Nhẹ nhàng đưa nút đảo gió về vị trí Stop
+5. Quan sát cánh quạt và đầu quạt trong 5 giây
+(Input: Quạt chạy tốc độ 1 và đang đảo gió; đưa nút đảo gió về vị trí Stop.)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1. Đầu quạt ngừng đảo qua lại và giữ tại một hướng ổn định
+2. Cánh quạt vẫn tiếp tục quay ở tốc độ 1 và tạo gió
+3. Không có tiếng kẹt, va đập hoặc rung bất thường
+4. Nút điều khiển không bị kẹt</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Như expected</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>23120031</t>
         </is>
       </c>
-      <c r="I19" s="3" t="n"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="I20" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>AI đã bỏ qua toàn bộ chức năng đảo gió vì không xác định được chức năng này từ ảnh.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/k21fPitYVVc?feature=share</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="G2:G19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Untested"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
